--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487145_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487145_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5557</v>
+        <v>3.1786</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7749</v>
+        <v>1.1741</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7808</v>
+        <v>2.0045</v>
       </c>
       <c r="G2" t="n">
         <v>2.8068</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9347</v>
+        <v>0.5575</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3517</v>
+        <v>-0.2491</v>
       </c>
       <c r="U2" t="n">
-        <v>1.583</v>
+        <v>0.8067</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5717</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0842</v>
+        <v>3.0376</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2967</v>
+        <v>1.1966</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7874</v>
+        <v>1.841</v>
       </c>
       <c r="G3" t="n">
         <v>3.6275</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1573</v>
+        <v>-0.2039</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1111</v>
+        <v>-0.0575</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2732</v>
+        <v>1.9183</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2953</v>
+        <v>-0.677</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5685</v>
+        <v>2.5953</v>
       </c>
       <c r="G4" t="n">
         <v>0.5737</v>
@@ -766,13 +766,13 @@
         <v>3.4741</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.2565</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5447</v>
+        <v>0.163</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0667</v>
+        <v>0.0935</v>
       </c>
       <c r="V4" t="n">
         <v>-1.228</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. CARTÓN CHARFOLE</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2829</v>
+        <v>1.8125</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1462</v>
+        <v>-0.8981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1367</v>
+        <v>2.7106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6524</v>
+        <v>-3.6639</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7399</v>
+        <v>-0.1895</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0875</v>
+        <v>-3.4744</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1125</v>
+        <v>-2.7774</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7801</v>
+        <v>0.512</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6676</v>
+        <v>-3.2894</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4601</v>
+        <v>-0.8865</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0403</v>
+        <v>-0.7015</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4199</v>
+        <v>-0.185</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
+        <v>-3.0881</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.6672</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.5863</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.5162</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.0701</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.4836</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.4836</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3511</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.7628</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.5803</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.1825</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0422</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.5717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>R. CARTÓN CHARFOLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3708</v>
+        <v>1.6488</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0185</v>
+        <v>1.5656</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3893</v>
+        <v>0.0832</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6639</v>
+        <v>0.6524</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1895</v>
+        <v>1.7399</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.4744</v>
+        <v>-1.0875</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7774</v>
+        <v>1.1125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.512</v>
+        <v>1.7801</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.2894</v>
+        <v>-0.6676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8865</v>
+        <v>-0.4601</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7015</v>
+        <v>-0.0403</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.185</v>
+        <v>-0.4199</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6672</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0279</v>
+        <v>-0.3969</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6366</v>
+        <v>-0.1609</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3913</v>
+        <v>-0.236</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4836</v>
+        <v>0.0422</v>
       </c>
       <c r="W6" t="n">
-        <v>5.4836</v>
+        <v>0.614</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0386</v>
+        <v>-0.0011</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2598</v>
+        <v>0.0595</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2212</v>
+        <v>-0.0606</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0177</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0912</v>
+        <v>0.0516</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2512</v>
+        <v>0.0509</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.16</v>
+        <v>0.0007</v>
       </c>
       <c r="V7" t="n">
         <v>-0.614</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6691</v>
+        <v>-1.3416</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3836</v>
+        <v>-2.314</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2855</v>
+        <v>0.9724</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.4147</v>
+        <v>-0.8265</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1077</v>
+        <v>-0.5609</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.307</v>
+        <v>-0.2656</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.747</v>
+        <v>-0.2462</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4197</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3273</v>
+        <v>-0.774</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6677</v>
+        <v>-0.5803</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6881</v>
+        <v>-1.0886</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9797</v>
+        <v>0.5084</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8951</v>
+        <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1699</v>
+        <v>-0.4452</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1151</v>
+        <v>-0.5816</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2849</v>
+        <v>0.1365</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1435</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3714</v>
+        <v>-0.3281</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0485</v>
+        <v>-1.7702</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8336</v>
+        <v>-1.565</v>
       </c>
       <c r="F9" t="n">
-        <v>0.785</v>
+        <v>-0.2052</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8265</v>
+        <v>-3.4147</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5609</v>
+        <v>-1.1077</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2656</v>
+        <v>-2.307</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2462</v>
+        <v>-1.747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.4197</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.774</v>
+        <v>-1.3273</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5803</v>
+        <v>-1.6677</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0886</v>
+        <v>-0.6881</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5084</v>
+        <v>-0.9797</v>
       </c>
       <c r="P9" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3161</v>
+        <v>2.8951</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1521</v>
+        <v>-0.271</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1012</v>
+        <v>-0.0664</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0509</v>
+        <v>-0.2046</v>
       </c>
       <c r="V9" t="n">
+        <v>1.1435</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.3714</v>
+      </c>
+      <c r="X9" t="n">
         <v>-1.228</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.3281</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.8999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,16 +1189,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>7.8878</v>
+        <v>8.482899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0534</v>
+        <v>-1.458299999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>9.940999999999999</v>
+        <v>9.941199999999998</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2624000000000004</v>
+        <v>-0.2623999999999995</v>
       </c>
       <c r="H10" t="n">
         <v>4.507200000000001</v>
@@ -1207,13 +1207,13 @@
         <v>-4.7697</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2021</v>
+        <v>3.202099999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>7.714300000000001</v>
+        <v>7.7143</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.5123</v>
+        <v>-4.512300000000001</v>
       </c>
       <c r="M10" t="n">
         <v>-3.4645</v>
@@ -1222,7 +1222,7 @@
         <v>-3.2072</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2573</v>
+        <v>-0.2573000000000001</v>
       </c>
       <c r="P10" t="n">
         <v>6.7552</v>
@@ -1234,22 +1234,22 @@
         <v>18.3358</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6327</v>
+        <v>-1.0377</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1016</v>
+        <v>-1.5067</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4690000000000001</v>
+        <v>0.4692</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0276</v>
+        <v>3.027600000000001</v>
       </c>
       <c r="W10" t="n">
         <v>8.4268</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.3991</v>
+        <v>-5.399100000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.9672</v>
+        <v>5.0156</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7776</v>
+        <v>1.5759</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1896</v>
+        <v>3.4397</v>
       </c>
       <c r="G11" t="n">
         <v>2.464</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3175</v>
+        <v>1.3659</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2718</v>
+        <v>0.0701</v>
       </c>
       <c r="U11" t="n">
-        <v>2.0457</v>
+        <v>1.2958</v>
       </c>
       <c r="V11" t="n">
         <v>1.1857</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5579</v>
+        <v>2.4922</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6681</v>
+        <v>1.4693</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8898</v>
+        <v>1.023</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2372</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4449</v>
+        <v>0.4895</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0271</v>
+        <v>-0.226</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5823</v>
+        <v>0.7155</v>
       </c>
       <c r="V12" t="n">
         <v>3.398</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0415</v>
+        <v>0.828</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5422</v>
+        <v>1.1416</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5007</v>
+        <v>-0.3136</v>
       </c>
       <c r="G13" t="n">
         <v>0.8332000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>0.386</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4363</v>
+        <v>0.2228</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5486</v>
+        <v>0.1481</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1124</v>
+        <v>0.0747</v>
       </c>
       <c r="V13" t="n">
         <v>-0.614</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.4642</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9954</v>
+        <v>-0.8952</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0921</v>
+        <v>1.3594</v>
       </c>
       <c r="G14" t="n">
         <v>1.7924</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2518</v>
+        <v>0.1157</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1051</v>
+        <v>0.3725</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2859</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6704</v>
+        <v>-0.17</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.371</v>
+        <v>-1.8703</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7006</v>
+        <v>1.7002</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8046</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4449</v>
+        <v>0.0555</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9082</v>
+        <v>-0.4075</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4633</v>
+        <v>0.463</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0382</v>
+        <v>-1.1293</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2016</v>
+        <v>-1.8011</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1635</v>
+        <v>0.6718</v>
       </c>
       <c r="G16" t="n">
         <v>-3.0388</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4204</v>
+        <v>0.4885</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.419</v>
+        <v>-0.0185</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0013</v>
+        <v>0.507</v>
       </c>
       <c r="V16" t="n">
         <v>1.228</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1301</v>
+        <v>-2.3846</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9614</v>
+        <v>-1.6588</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1687</v>
+        <v>-0.7259</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9967</v>
+        <v>0.1365</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5472</v>
+        <v>-0.7524</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5505</v>
+        <v>0.889</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6963</v>
+        <v>0.6502</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1915</v>
+        <v>-0.6521</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5048</v>
+        <v>1.3024</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3004</v>
+        <v>-0.5137</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3557</v>
+        <v>-0.1003</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0553</v>
+        <v>-0.4134</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8666</v>
+        <v>0.1001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.665</v>
+        <v>0.2773</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2016</v>
+        <v>-0.1772</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.228</v>
+        <v>-1.2702</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2984</v>
+        <v>-2.4706</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3584</v>
+        <v>-1.2018</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.2688</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1365</v>
+        <v>-0.2592</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7524</v>
+        <v>0.3498</v>
       </c>
       <c r="I18" t="n">
-        <v>0.889</v>
+        <v>-0.6091</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6502</v>
+        <v>-0.2457</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6521</v>
+        <v>1.0245</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3024</v>
+        <v>-1.2702</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5137</v>
+        <v>-0.0135</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1003</v>
+        <v>-0.6747</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4134</v>
+        <v>0.6612</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1864</v>
+        <v>-0.0486</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5777</v>
+        <v>0.0089</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3913</v>
+        <v>-0.0575</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2702</v>
+        <v>-2.7418</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.614</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.079</v>
+        <v>-2.7779</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.302</v>
+        <v>-2.6624</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.777</v>
+        <v>-0.1155</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2592</v>
+        <v>-0.9967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3498</v>
+        <v>-1.5472</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6091</v>
+        <v>0.5505</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2457</v>
+        <v>-0.6963</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0245</v>
+        <v>-0.1915</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2702</v>
+        <v>-0.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0135</v>
+        <v>-0.3004</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6747</v>
+        <v>-1.3557</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6612</v>
+        <v>1.0553</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.657</v>
+        <v>0.2188</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0912</v>
+        <v>-0.036</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5658</v>
+        <v>0.2548</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.7418</v>
+        <v>-1.228</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.7418</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6646</v>
+        <v>-2.8232</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1063</v>
+        <v>0.7071</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7709</v>
+        <v>-3.5303</v>
       </c>
       <c r="G20" t="n">
         <v>0.0026</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9677</v>
+        <v>-0.1262</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5658</v>
+        <v>0.0351</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4019</v>
+        <v>-0.1613</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6996</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6704</v>
+        <v>-3.597</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8456</v>
+        <v>-4.7455</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1753</v>
+        <v>1.1485</v>
       </c>
       <c r="G21" t="n">
         <v>0.3703</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0126</v>
+        <v>0.0859</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1639</v>
+        <v>-0.0638</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1765</v>
+        <v>0.1497</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.887799999999999</v>
+        <v>-6.5526</v>
       </c>
       <c r="E22" t="n">
         <v>-9.941199999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0536</v>
+        <v>3.3885</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2624999999999996</v>
+        <v>0.2624999999999994</v>
       </c>
       <c r="H22" t="n">
         <v>-4.5072</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7699</v>
+        <v>4.769899999999999</v>
       </c>
       <c r="J22" t="n">
         <v>3.4645</v>
@@ -2149,13 +2149,13 @@
         <v>3.2075</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2571999999999998</v>
+        <v>0.2571999999999997</v>
       </c>
       <c r="M22" t="n">
         <v>-3.2021</v>
       </c>
       <c r="N22" t="n">
-        <v>-7.714399999999999</v>
+        <v>-7.7144</v>
       </c>
       <c r="O22" t="n">
         <v>4.512599999999999</v>
@@ -2170,13 +2170,13 @@
         <v>11.5803</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6327</v>
+        <v>2.9679</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4689999999999996</v>
+        <v>-0.4690999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1018</v>
+        <v>3.437</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0278</v>
